--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A5/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1452" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11D1E308-0B4E-45B6-9F35-8ABC406CA317}"/>
+  <xr:revisionPtr revIDLastSave="1459" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA0997B5-2F2E-4A37-8EE5-1F25B2A220DD}"/>
   <bookViews>
-    <workbookView xWindow="14376" yWindow="1572" windowWidth="8712" windowHeight="10404" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15528" yWindow="2676" windowWidth="7188" windowHeight="9852" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YTD Profit" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="5">
   <si>
     <t>Date</t>
   </si>
@@ -147,10 +147,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -450,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I191"/>
+  <dimension ref="A1:I197"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -3343,6 +3339,47 @@
         <v>-1067000</v>
       </c>
     </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B193" s="4">
+        <v>45989</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B194" s="6">
+        <v>-948000</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B195" s="7">
+        <v>333000</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B196" s="6">
+        <v>503000</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B197" s="8">
+        <f>B194+B195-B196</f>
+        <v>-1118000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
